--- a/artfynd/A 40067-2021 artfynd.xlsx
+++ b/artfynd/A 40067-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40067-2021 artfynd.xlsx
+++ b/artfynd/A 40067-2021 artfynd.xlsx
@@ -675,45 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>71562115</v>
+        <v>71562114</v>
       </c>
       <c r="B2" t="n">
-        <v>98539</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103691</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224913</v>
+        <v>222009</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Viola rupestris</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -725,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>420725.0911902498</v>
+        <v>420746</v>
       </c>
       <c r="R2" t="n">
-        <v>6442981.775536012</v>
+        <v>6442980</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,19 +748,9 @@
           <t>2018-05-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-05-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,40 +777,40 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>71562114</v>
+        <v>71562115</v>
       </c>
       <c r="B3" t="n">
-        <v>101128</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222009</v>
+        <v>224913</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Vanlig backsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Viola rupestris</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>F. W. Schmidt</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -842,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>420746.2247496236</v>
+        <v>420725</v>
       </c>
       <c r="R3" t="n">
-        <v>6442979.768963025</v>
+        <v>6442982</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,19 +855,9 @@
           <t>2018-05-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-05-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
